--- a/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
+++ b/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="B2:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="62" min="1" max="1"/>
@@ -1261,7 +1261,6 @@
     <col width="96" customWidth="1" style="62" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="15" customHeight="1" s="63">
       <c r="B2" s="64" t="inlineStr">
         <is>
@@ -1276,7 +1275,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="63">
       <c r="B5" s="66" t="inlineStr">
         <is>
@@ -1425,7 +1423,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="63">
       <c r="B18" s="68" t="inlineStr">
         <is>
@@ -1433,7 +1430,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="25.5" customHeight="1" s="63">
       <c r="B20" s="69" t="inlineStr">
         <is>
@@ -2851,10 +2847,14 @@
       </c>
       <c r="J25" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K25" s="75" t="n"/>
+          <t>Finalizada</t>
+        </is>
+      </c>
+      <c r="K25" s="75" t="inlineStr">
+        <is>
+          <t>Entregado: Entregable_semana_19.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="42.75" customHeight="1" s="63">
       <c r="A26" s="72" t="n">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="J26" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Finalizada</t>
         </is>
       </c>
       <c r="K26" s="67" t="inlineStr">
         <is>
-          <t>Núcleo del aporte del proyecto; no se recorta. Hito H5</t>
+          <t>Núcleo del aporte del proyecto; no se recorta. Hito H5. Ejecutada y medida el 2026-08-30: S21_relevo_ejecutado.md</t>
         </is>
       </c>
     </row>
@@ -3114,10 +3114,14 @@
       </c>
       <c r="J30" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K30" s="67" t="n"/>
+          <t>Finalizada</t>
+        </is>
+      </c>
+      <c r="K30" s="67" t="inlineStr">
+        <is>
+          <t>Entregado: Entregable_semana_20.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="42.75" customHeight="1" s="63">
       <c r="A31" s="74" t="n">
@@ -3377,10 +3381,14 @@
       </c>
       <c r="J35" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K35" s="75" t="n"/>
+          <t>Finalizada</t>
+        </is>
+      </c>
+      <c r="K35" s="75" t="inlineStr">
+        <is>
+          <t>Entregado: Entregable_semana_21.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1" s="63">
       <c r="A36" s="72" t="n">
@@ -3538,12 +3546,12 @@
       </c>
       <c r="J38" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Finalizada</t>
         </is>
       </c>
       <c r="K38" s="67" t="inlineStr">
         <is>
-          <t>Hito H7</t>
+          <t>Hito H7. Etiqueta v0.4-implementacion-congelada en el repositorio</t>
         </is>
       </c>
     </row>
@@ -3593,10 +3601,14 @@
       </c>
       <c r="J39" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K39" s="75" t="n"/>
+          <t>Finalizada</t>
+        </is>
+      </c>
+      <c r="K39" s="75" t="inlineStr">
+        <is>
+          <t>Entregado: Entregable_semana_22.tex (la fuente es el entregable versionado)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="42.75" customHeight="1" s="63">
       <c r="A40" s="72" t="n">
@@ -3644,12 +3656,12 @@
       </c>
       <c r="J40" s="78" t="inlineStr">
         <is>
-          <t>Reprogramada</t>
+          <t>Finalizada</t>
         </is>
       </c>
       <c r="K40" s="67" t="inlineStr">
         <is>
-          <t>Ejecución de pruebas de evaluación: Cap. 8 S20–S22 → S24–S25. Decisión D1</t>
+          <t>Ejecución de pruebas de evaluación: Cap. 8 S20–S22 → S24–S25. Decisión D1. 30 registros del 2026-09-05 en Documentos/Evidencia/registros</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8585,7 @@
       </c>
       <c r="H6" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Finalizada</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8669,7 @@
       </c>
       <c r="H8" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Finalizada</t>
         </is>
       </c>
     </row>

--- a/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
+++ b/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
@@ -2796,10 +2796,14 @@
       </c>
       <c r="J24" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K24" s="67" t="n"/>
+          <t>Superada</t>
+        </is>
+      </c>
+      <c r="K24" s="67" t="inlineStr">
+        <is>
+          <t>Superada: el mapa real existe (mapas/mapa_laboratorio.pgm, 8,45 x 6,90 m de contenido, sacado con map_saver_cli sobre el vehiculo). El criterio no es aplicable: verificar_mapa.py compara contra un .world y un laboratorio fisico no tiene. S20_frente_b_hardware.md §5</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="63">
       <c r="A25" s="74" t="n">
@@ -2932,7 +2936,7 @@
       </c>
       <c r="E27" s="75" t="inlineStr">
         <is>
-          <t>Campos añadidos al registro CSV, con las cuatro métricas completas</t>
+          <t>Campos anadidos al registro de mision (JSON), con las cuatro metricas completas</t>
         </is>
       </c>
       <c r="F27" s="74" t="inlineStr">
@@ -2957,10 +2961,14 @@
       </c>
       <c r="J27" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K27" s="75" t="n"/>
+          <t>Finalizada</t>
+        </is>
+      </c>
+      <c r="K27" s="75" t="inlineStr">
+        <is>
+          <t>Finalizada: RF-23, RF-24, RF-25 y RF-26 verificados sobre las 30 misiones de la campana (2026-09-04/05)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="63">
       <c r="A28" s="72" t="n">
@@ -3011,7 +3019,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="K28" s="67" t="n"/>
+      <c r="K28" s="67" t="inlineStr">
+        <is>
+          <t>Bloqueada el 2026-09-21: el vehiculo no tiene topico /cmd_vel y servo_pkg dejo de atender tras una perdida de potencia de traccion (S24_actuacion_bloqueada_servo.md)</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="42.75" customHeight="1" s="63">
       <c r="A29" s="74" t="n">
@@ -3059,12 +3071,12 @@
       </c>
       <c r="J29" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En ejecución</t>
         </is>
       </c>
       <c r="K29" s="75" t="inlineStr">
         <is>
-          <t>El cronograma no se renegocia; se consume holgura de alcance</t>
+          <t>El cronograma no se renegocia; se consume holgura de alcance. Se resuelve en S24 (21-27 sep): se deja de posponer. Su requisito previo (act. 27) esta bloqueado porque la cadena de actuacion del vehiculo no responde (S24_actuacion_bloqueada_servo.md); la decision se toma CON ese dato, no esperando a que se desbloquee</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3156,7 @@
       </c>
       <c r="E31" s="75" t="inlineStr">
         <is>
-          <t>Directorio «hri/» en el repositorio y captura desde el navegador de un teléfono</t>
+          <t>Directorio «interfaz_web/» en el repositorio y operacion desde el navegador de un telefono</t>
         </is>
       </c>
       <c r="F31" s="74" t="inlineStr">
@@ -3169,12 +3181,12 @@
       </c>
       <c r="J31" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Finalizada</t>
         </is>
       </c>
       <c r="K31" s="75" t="inlineStr">
         <is>
-          <t>Decisión D5: es una desviación frente a «aplicación móvil» y se declara</t>
+          <t>Decisión D5: es una desviación frente a «aplicación móvil» y se declara. Finalizada: interfaz_web/ esta en main y RF-20 se verifico el 2026-09-10 en un telefono real (SSID DEEPRACER, WebSocket establecido). El producto nombraba un directorio «hri/» que nunca existio</t>
         </is>
       </c>
     </row>
@@ -3224,10 +3236,14 @@
       </c>
       <c r="J32" s="77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K32" s="67" t="n"/>
+          <t>Finalizada</t>
+        </is>
+      </c>
+      <c r="K32" s="67" t="inlineStr">
+        <is>
+          <t>Finalizada: RF-17, RF-18 y RF-19 verificados el 2026-09-02 contra el coordinador real; RF-28 graba la solicitud con su mision_id</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="63">
       <c r="A33" s="74" t="n">
@@ -3333,7 +3349,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="K34" s="67" t="n"/>
+      <c r="K34" s="67" t="inlineStr">
+        <is>
+          <t>Bloqueada aguas arriba: depende del GO/NO-GO (act. 28) y de la actuacion del vehiculo</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="63">
       <c r="A35" s="74" t="n">
@@ -3436,12 +3456,12 @@
       </c>
       <c r="J36" s="78" t="inlineStr">
         <is>
-          <t>Reprogramada</t>
+          <t>Superada</t>
         </is>
       </c>
       <c r="K36" s="67" t="inlineStr">
         <is>
-          <t>Verificación general: Cap. 8 S16–S18 → S23. Corrección de fallas: S18–S20 → S23</t>
+          <t>Verificación general: Cap. 8 S16–S18 → S23. Corrección de fallas: S18–S20 → S23. Superada: depende de la act. 32, aun reprogramada. La verificacion que si se hizo audita el metodo, no las fallas: S22_barrido_criterios_infalsables.md (2026-09-11)</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3516,7 @@
       </c>
       <c r="K37" s="75" t="inlineStr">
         <is>
-          <t>Pruebas en condiciones controladas: Cap. 8 S17–S20 → S23–S25</t>
+          <t>Pruebas en condiciones controladas: Cap. 8 S17–S20 → S23–S25. Bloqueada aguas arriba: depende del despliegue (act. 33)</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3706,7 @@
       </c>
       <c r="E41" s="75" t="inlineStr">
         <is>
-          <t>Directorio «resultados/» versionado y documentado</t>
+          <t>Directorio «Documentos/Evidencia/registros/» versionado y documentado</t>
         </is>
       </c>
       <c r="F41" s="74" t="inlineStr">
@@ -3711,12 +3731,12 @@
       </c>
       <c r="J41" s="78" t="inlineStr">
         <is>
-          <t>Reprogramada</t>
+          <t>Finalizada</t>
         </is>
       </c>
       <c r="K41" s="75" t="inlineStr">
         <is>
-          <t>Recolección de información: Cap. 8 S21–S23 → S24–S25; se fusiona con la ejecución mediante registro automático</t>
+          <t>Recolección de información: Cap. 8 S21–S23 → S24–S25; se fusiona con la ejecución mediante registro automático. Finalizada el 2026-09-21 (S24_consolidacion_datos_oe4.md): los 30 registros regeneran las metricas publicadas, 13/13 bloques identicos. El producto nombraba un directorio «resultados/» que nunca existio</t>
         </is>
       </c>
     </row>

--- a/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
+++ b/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="E29" s="75" t="inlineStr">
         <is>
-          <t>Acta de decisión firmada por los autores y comunicada a los directores</t>
+          <t>Acta de decision firmada por los autores y comunicada a los directores: Documentos/ACTA_GO_NOGO.md</t>
         </is>
       </c>
       <c r="F29" s="74" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="K29" s="75" t="inlineStr">
         <is>
-          <t>El cronograma no se renegocia; se consume holgura de alcance. Se resuelve en S24 (21-27 sep): se deja de posponer. Su requisito previo (act. 27) esta bloqueado porque la cadena de actuacion del vehiculo no responde (S24_actuacion_bloqueada_servo.md); la decision se toma CON ese dato, no esperando a que se desbloquee</t>
+          <t>El cronograma no se renegocia; se consume holgura de alcance. Se resuelve en S24 (21-27 sep): se deja de posponer. Su requisito previo (act. 27) esta bloqueado porque la cadena de actuacion del vehiculo no responde (S24_actuacion_bloqueada_servo.md); la decision se toma CON ese dato, no esperando a que se desbloquee. Acta redactada el 2026-09-21: GO PLENO (los dos vehiculos reales), con seis criterios de fallo escritos antes de correr y cuatro cortes con fecha; el ultimo, el 16 de octubre, cierra la toma de datos. Pendiente de firma de ambos autores y de comunicar a los directores</t>
         </is>
       </c>
     </row>

--- a/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
+++ b/Documentos/Entregables/Actividad_1_Corte_1_Cronograma_2026-2.xlsx
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C7" s="67" t="inlineStr">
         <is>
-          <t>Ing. Armando Mateus Rojas, Msc. · Ing. Nestor Ivan Ospina, Msc. · Ing. Oscar Mauricio Gélvez Lizarazo, Msc.</t>
+          <t>Ing. Armando Mateus Rojas, Msc.</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="K6" s="67" t="inlineStr">
         <is>
-          <t>Constancia de revisión firmada por Armando Mateus el 2026-08-14, dentro del plazo. Firma un solo director, no los tres. D3 y D4 se revisaron el 2026-08-15, después de la firma: se comunican en este corte</t>
+          <t>Constancia de revisión firmada por Armando Mateus el 2026-08-14, dentro del plazo. D3 y D4 se revisaron el 2026-08-15, después de la firma: se comunican en este corte</t>
         </is>
       </c>
     </row>
